--- a/data/trans_bre/IP12-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 1,61</t>
+          <t>-10,58; 1,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 9,15</t>
+          <t>-4,83; 8,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 14,91</t>
+          <t>1,34; 14,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 11,76</t>
+          <t>-0,12; 12,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 34,1</t>
+          <t>-77,29; 27,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 239,47</t>
+          <t>-45,95; 206,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 888,93</t>
+          <t>10,28; 720,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 500,87</t>
+          <t>-13,47; 493,98</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 6,78</t>
+          <t>-5,93; 7,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 14,07</t>
+          <t>0,24; 14,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,13</t>
+          <t>-7,98; 2,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 0,38</t>
+          <t>-14,06; -0,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 186,42</t>
+          <t>-62,51; 192,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 451,22</t>
+          <t>-4,8; 439,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,28; 50,94</t>
+          <t>-74,28; 47,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,56; 16,34</t>
+          <t>-85,86; 10,71</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 6,0</t>
+          <t>-6,09; 6,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 6,89</t>
+          <t>-7,1; 6,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 8,12</t>
+          <t>-6,1; 8,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 5,72</t>
+          <t>-8,69; 4,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 137,62</t>
+          <t>-66,36; 192,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 128,4</t>
+          <t>-58,28; 126,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,08; 247,96</t>
+          <t>-64,64; 286,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,84; 185,77</t>
+          <t>-77,99; 156,08</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,61</t>
+          <t>-4,48; 3,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 3,09</t>
+          <t>-6,01; 3,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 5,1</t>
+          <t>-3,39; 5,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 1,12</t>
+          <t>-6,22; 1,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,51; 65,94</t>
+          <t>-46,43; 66,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,77; 44,02</t>
+          <t>-50,07; 44,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 83,23</t>
+          <t>-35,02; 87,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 29,99</t>
+          <t>-69,1; 28,16</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 8,92</t>
+          <t>-1,52; 8,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 6,35</t>
+          <t>-3,78; 6,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,63</t>
+          <t>-2,09; 7,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 8,07</t>
+          <t>-4,88; 7,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 331,32</t>
+          <t>-33,33; 304,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,05; 152,06</t>
+          <t>-44,23; 135,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 228,32</t>
+          <t>-33,07; 245,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 120,52</t>
+          <t>-37,91; 134,1</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 3,83</t>
+          <t>-7,03; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 3,9</t>
+          <t>-10,09; 4,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 6,4</t>
+          <t>-6,7; 7,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 6,39</t>
+          <t>-6,52; 6,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-84,99; 230,22</t>
+          <t>-85,66; 181,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,6; 90,92</t>
+          <t>-86,39; 134,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,64; 277,43</t>
+          <t>-77,56; 288,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,61; 216,14</t>
+          <t>-69,78; 235,74</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,74</t>
+          <t>-2,59; 1,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,31</t>
+          <t>-1,72; 3,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,46</t>
+          <t>-0,89; 3,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,81</t>
+          <t>-3,03; 2,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 31,6</t>
+          <t>-31,93; 28,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 47,59</t>
+          <t>-18,75; 44,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 66,15</t>
+          <t>-11,93; 72,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 29,28</t>
+          <t>-32,85; 33,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 1,27</t>
+          <t>-10,5; 1,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 8,96</t>
+          <t>-4,25; 9,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 14,04</t>
+          <t>1,55; 14,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 12,29</t>
+          <t>-0,09; 12,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,29; 27,06</t>
+          <t>-77,12; 29,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 206,85</t>
+          <t>-41,87; 255,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 720,93</t>
+          <t>14,28; 870,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 493,98</t>
+          <t>-11,14; 476,87</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 7,12</t>
+          <t>-5,77; 6,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 14,17</t>
+          <t>0,77; 14,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 2,05</t>
+          <t>-7,88; 2,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,06; -0,17</t>
+          <t>-14,21; -0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,51; 192,01</t>
+          <t>-58,18; 175,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 439,11</t>
+          <t>-1,64; 436,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 47,13</t>
+          <t>-76,81; 57,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,86; 10,71</t>
+          <t>-86,41; 12,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 6,38</t>
+          <t>-6,24; 6,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 6,98</t>
+          <t>-8,08; 6,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 8,13</t>
+          <t>-5,91; 8,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 4,97</t>
+          <t>-10,01; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 192,7</t>
+          <t>-68,39; 184,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 126,24</t>
+          <t>-61,45; 119,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 286,9</t>
+          <t>-66,4; 271,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-77,99; 156,08</t>
+          <t>-80,58; 152,4</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,51</t>
+          <t>-4,78; 2,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 3,24</t>
+          <t>-6,67; 2,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 5,35</t>
+          <t>-3,51; 5,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 1,32</t>
+          <t>-6,56; 1,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 66,56</t>
+          <t>-49,67; 52,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 44,54</t>
+          <t>-53,44; 40,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 87,13</t>
+          <t>-31,71; 82,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,1; 28,16</t>
+          <t>-71,14; 29,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 8,46</t>
+          <t>-1,45; 9,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 6,3</t>
+          <t>-4,16; 6,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 7,52</t>
+          <t>-2,51; 6,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 7,94</t>
+          <t>-4,87; 8,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 304,09</t>
+          <t>-27,88; 374,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,23; 135,98</t>
+          <t>-43,36; 154,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 245,71</t>
+          <t>-37,77; 211,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 134,1</t>
+          <t>-39,09; 130,78</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 3,61</t>
+          <t>-6,9; 3,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 4,84</t>
+          <t>-10,95; 4,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 7,19</t>
+          <t>-6,43; 6,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 6,71</t>
+          <t>-6,87; 6,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,66; 181,8</t>
+          <t>-85,99; 232,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,39; 134,08</t>
+          <t>-86,03; 129,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,56; 288,7</t>
+          <t>-77,73; 246,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 235,74</t>
+          <t>-69,38; 257,33</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,57</t>
+          <t>-2,76; 1,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,02</t>
+          <t>-1,58; 3,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,85</t>
+          <t>-1,05; 3,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,09</t>
+          <t>-3,02; 1,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 28,88</t>
+          <t>-33,19; 28,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 44,5</t>
+          <t>-17,25; 45,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 72,95</t>
+          <t>-13,84; 65,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 33,6</t>
+          <t>-34,06; 33,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>126,33%</t>
+          <t>128,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 1,48</t>
+          <t>-9,92; 1,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 9,36</t>
+          <t>-4,57; 9,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,9</t>
+          <t>1,38; 14,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 12,18</t>
+          <t>-0,31; 12,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,12; 29,89</t>
+          <t>-74,18; 34,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,87; 255,52</t>
+          <t>-47,49; 239,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 870,95</t>
+          <t>10,39; 888,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 476,87</t>
+          <t>-16,83; 486,13</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,12</t>
+          <t>-6,95</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-56,84%</t>
+          <t>-61,85%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,78</t>
+          <t>-6,15; 6,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 14,25</t>
+          <t>0,72; 14,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 2,65</t>
+          <t>-7,91; 2,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,21; -0,25</t>
+          <t>-14,51; -0,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 175,31</t>
+          <t>-59,49; 186,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 436,99</t>
+          <t>-2,73; 451,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,81; 57,77</t>
+          <t>-77,28; 50,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,41; 12,37</t>
+          <t>-86,77; 5,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-16,89%</t>
+          <t>-24,68%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,79</t>
+          <t>-6,84; 6,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 6,6</t>
+          <t>-7,17; 6,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 8,71</t>
+          <t>-6,59; 8,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 5,37</t>
+          <t>-9,88; 4,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 184,36</t>
+          <t>-69,18; 137,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 119,44</t>
+          <t>-58,96; 128,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-66,4; 271,71</t>
+          <t>-69,08; 247,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-80,58; 152,4</t>
+          <t>-81,7; 141,98</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,42</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-35,18%</t>
+          <t>-21,11%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,95</t>
+          <t>-4,76; 3,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 2,92</t>
+          <t>-6,01; 3,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 5,44</t>
+          <t>-3,56; 5,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,27</t>
+          <t>-5,57; 2,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,67; 52,76</t>
+          <t>-49,51; 65,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,44; 40,48</t>
+          <t>-48,77; 44,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 82,72</t>
+          <t>-34,27; 83,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 29,31</t>
+          <t>-60,4; 58,69</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 9,31</t>
+          <t>-2,1; 8,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 6,56</t>
+          <t>-3,77; 6,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,85</t>
+          <t>-2,24; 6,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 8,35</t>
+          <t>-6,5; 7,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 374,24</t>
+          <t>-37,85; 331,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 154,88</t>
+          <t>-45,05; 152,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 211,1</t>
+          <t>-38,42; 228,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 130,78</t>
+          <t>-47,83; 112,8</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>-1,78%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,95</t>
+          <t>-6,91; 3,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 4,85</t>
+          <t>-10,98; 3,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 6,55</t>
+          <t>-6,59; 6,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 6,69</t>
+          <t>-7,35; 6,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,99; 232,14</t>
+          <t>-84,99; 230,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,03; 129,8</t>
+          <t>-87,6; 90,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,73; 246,31</t>
+          <t>-78,64; 277,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,38; 257,33</t>
+          <t>-74,48; 225,27</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-7,19%</t>
+          <t>-5,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,66</t>
+          <t>-2,58; 1,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,2</t>
+          <t>-1,58; 3,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,65</t>
+          <t>-0,91; 3,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,99</t>
+          <t>-3,22; 1,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 28,46</t>
+          <t>-32,82; 31,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 45,56</t>
+          <t>-17,44; 47,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 65,48</t>
+          <t>-11,82; 66,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 33,33</t>
+          <t>-33,96; 29,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-4,06</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-42,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>190,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>128,98%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-4.062934196063187</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.235500421604796</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.57878130734427</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>6.186876121529637</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.4243108915233735</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.303438830685024</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.900193232793727</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.289784476115861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,92; 1,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,57; 9,15</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,38; 14,91</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-0,31; 12,16</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-74,18; 34,1</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-47,49; 239,47</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,39; 888,93</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-16,83; 486,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.915454652189554</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.570011390043262</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.380539077045831</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.3117994443405223</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7418340276757461</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.474881205885431</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.103900685187437</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1683466502713732</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.60748411180457</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.149088952858881</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>14.91328633494741</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>12.16012577311235</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3409622747958853</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.394676700531651</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>8.889343048913052</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>4.86128059465082</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,97</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,95</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>125,51%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-38,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-61,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,15; 6,78</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,72; 14,07</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,91; 2,13</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-14,51; -0,54</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-59,49; 186,42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-2,73; 451,22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-77,28; 50,94</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-86,77; 5,18</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.4346096097567226</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7.242673612499753</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.973009020606036</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-6.947474290865016</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.06166438921769219</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.255071793539372</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3835305931853091</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.6184975093821129</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-24,68%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.148004173520764</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.718922288723005</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.910376045134393</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-14.50989437770114</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5948529241113365</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.02733671892512261</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7727565389344584</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.8677054978669664</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,84; 6,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 6,89</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 8,12</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,88; 4,51</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-69,18; 137,62</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-58,96; 128,4</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-69,08; 247,96</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-81,7; 141,98</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.779723373190248</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>14.06688369155968</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.126774353982868</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.5412369130253529</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.864228729269006</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.512239624025555</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.509407435312742</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.05184714176938443</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-9,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-14,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-21,11%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4412989770530992</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.2590793626870008</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6590616446425196</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.822604582375326</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.0638246956620077</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.02871870140334262</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.09881223325269442</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2468162815207827</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 3,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,01; 3,09</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,56; 5,1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,57; 2,54</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-49,51; 65,94</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-48,77; 44,02</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-34,27; 83,23</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-60,4; 58,69</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.839353684150727</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.166530754848452</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.589228101949807</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.884388641067316</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6917680018133106</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5895509409720163</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6908329641715917</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.8169905847399151</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.00254179449536</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.892581294828876</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.122065395919941</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.505182296073302</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.376229030701595</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.284018793882532</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.479633674694735</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.419762904643129</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,18</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>67,31%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 8,92</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,77; 6,35</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,24; 6,63</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-6,5; 7,37</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-37,85; 331,32</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-45,05; 152,06</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-38,42; 228,32</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-47,83; 112,8</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.6850814962465355</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.483230552334132</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8918384036689375</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.428218890930671</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.09045613574339914</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1497146038929993</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1074447503819988</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2111096827198248</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-3,25</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-29,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-37,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-2,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-1,78%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.756841902291049</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.005269480739826</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.555523231726272</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.573629400471722</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4951234509202814</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4877146344792257</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3427396501379941</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6039611391196134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-6,91; 3,83</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-10,98; 3,9</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-6,59; 6,4</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,35; 6,48</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-84,99; 230,22</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-87,6; 90,92</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-78,64; 277,43</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-74,48; 225,27</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.611859638349945</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.090511764530845</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.104490169564576</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.540930470734996</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.65944036201946</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.4401551154354711</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.8323435872522696</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5868643338037727</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-5,3%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>3.178688077449283</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.298702295111621</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.348212469821667</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.9014174659341595</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.6731453675542745</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1907470716765571</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.4520842105619937</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.09103722820751238</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 1,74</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,58; 3,31</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,91; 3,46</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,22; 1,86</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-32,82; 31,6</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-17,44; 47,59</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-11,82; 66,15</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-33,96; 29,18</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.104325091475106</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.771171559306291</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.242356774667485</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.498345544312201</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3785009170594026</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4505346745960744</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.384248689592138</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4783438359569193</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8.915315830465863</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.347650048688962</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.628618742977174</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.37477423015621</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>3.313206728667186</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.520609321458588</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.283235529292138</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.128027587520889</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-1.563594573457368</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-3.254533484508804</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-0.1535694472296865</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-0.1210510310499957</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2971147937955468</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.3765606425041208</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.0268049460085604</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.01782157158208817</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-6.91486831015054</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-10.97872690646626</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-6.587156403503807</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-7.34947271196608</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.8498826791851503</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8759906904656036</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.786425180364987</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.7447528923422122</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.825576584706287</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3.895893751368718</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>6.402372283030135</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>6.476249640086452</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>2.302180202007288</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.9092181809965937</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2.774281905056409</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>2.252727413976328</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.4302320493458356</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.760674182171564</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.397299454026141</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.4103398495221608</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.06214885844430823</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.09296450841838634</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.2129479529402456</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.05304395692568602</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.580701709704711</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.579878589961791</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.9116964066496532</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-3.215774135460349</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.3281598500923514</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1743629353425123</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1182397186277096</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3396338930351012</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.743233949488672</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.312313124586826</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.464649187794284</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.861359767131952</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.316014364534255</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.475932036315176</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.6614676465393156</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.2917701103718411</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
